--- a/business_forms/047_dealership_inventory_registration_form--business_forms.xlsx
+++ b/business_forms/047_dealership_inventory_registration_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>make</t>
+          <t>vehicle_make</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>make</t>
+          <t>Vehicle Make</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>vehicle_model</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>Vehicle Model</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>vehicle_year</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>Vehicle Year</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,40 +584,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>is_available_for_purchase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>Is Vehicle Available for Purchase?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>select_one_make</t>
+          <t>register_multiple_models</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>make</t>
+          <t>Register Multiple Models?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>select_multiple_models</t>
+          <t>is_available_forimmediate_delivery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>Is Vehicle Available for Immediate Delivery?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,63 +653,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>select_one_year</t>
+          <t>vehicle_note</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>register_immediately</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Register Vehicle Immediately?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>is_vehicle_available_for_trade_in</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Is Vehicle Available for Trade-in?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,159 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>is_vehicle_in_good_condition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Is Vehicle in Good Condition?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_one_make</t>
+          <t>vehicle_delivery_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>make</t>
+          <t>Vehicle Delivery Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_multiple_models</t>
+          <t>vehicle_delivery_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>Vehicle Delivery Time</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>select_one_year</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -891,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -919,177 +827,177 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_one_make_choices</t>
+          <t>is_available_for_purchase_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'toyota'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Toyota'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_one_make_choices</t>
+          <t>is_available_for_purchase_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'honda'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Honda'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one_make_choices</t>
+          <t>register_multiple_models_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'ford'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Ford'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple_models_choices</t>
+          <t>register_multiple_models_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'corolla'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Corolla'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple_models_choices</t>
+          <t>is_available_forimmediate_delivery_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'accord'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Accord'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple_models_choices</t>
+          <t>is_available_forimmediate_delivery_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'mustang'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Mustang'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_models_choices</t>
+          <t>register_immediately_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'explorer'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Explorer'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_year_choices</t>
+          <t>register_immediately_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_2015}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 2015}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_year_choices</t>
+          <t>is_vehicle_available_for_trade_in_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_2016}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 2016}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_year_choices</t>
+          <t>is_vehicle_available_for_trade_in_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_2017}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 2017}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one_make_choices</t>
+          <t>is_vehicle_in_good_condition_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1106,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one_make_choices</t>
+          <t>is_vehicle_in_good_condition_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1115,74 +1023,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple_models_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple_models_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one_year_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one_year_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
